--- a/examples/example-barcodes.xlsx
+++ b/examples/example-barcodes.xlsx
@@ -4,72 +4,21 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Barcodes" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Barcodes" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>PROD-001</t>
-  </si>
-  <si>
-    <t>PROD-002</t>
-  </si>
-  <si>
-    <t>PROD-003</t>
-  </si>
-  <si>
-    <t>ITEM-A100</t>
-  </si>
-  <si>
-    <t>ITEM-B200</t>
-  </si>
-  <si>
-    <t>ITEM-C300</t>
-  </si>
-  <si>
-    <t>SKU-12345</t>
-  </si>
-  <si>
-    <t>SKU-67890</t>
-  </si>
-  <si>
-    <t>INV-2024-01</t>
-  </si>
-  <si>
-    <t>INV-2024-02</t>
-  </si>
-  <si>
-    <t>BOX-A1</t>
-  </si>
-  <si>
-    <t>BOX-A2</t>
-  </si>
-  <si>
-    <t>BOX-B1</t>
-  </si>
-  <si>
-    <t>BOX-B2</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,11 +41,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -119,11 +65,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="797039" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -158,11 +104,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="797039" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -197,11 +143,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="797039" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -236,11 +182,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="849630" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -275,11 +221,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>14999</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="849630" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 5">
@@ -314,11 +260,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>14999</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="849630" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Picture 6">
@@ -353,11 +299,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>14999</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="797039" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Picture 7">
@@ -392,11 +338,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="797039" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Picture 8">
@@ -431,11 +377,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="849630" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Picture 9">
@@ -470,11 +416,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="849630" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Picture 10">
@@ -509,11 +455,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>15000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="654480" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Picture 11">
@@ -548,11 +494,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>14999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="654480" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="12" name="Picture 12">
@@ -587,11 +533,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>14999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="654480" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="13" name="Picture 13">
@@ -626,11 +572,11 @@
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>14999</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="809625" cy="333375"/>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="654480" cy="323999"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="14" name="Picture 14">
@@ -987,60 +933,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
+    <row r="1" ht="28.3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" ht="28.3" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
